--- a/output/pdf_financials_xlsx/MHUB.xlsx
+++ b/output/pdf_financials_xlsx/MHUB.xlsx
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.456179</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.940996</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.153102</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.869376</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.2622</v>
       </c>
     </row>
     <row r="35">
@@ -1212,19 +1212,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.456179</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.940996</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.153102</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.869376</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.2622</v>
       </c>
     </row>
     <row r="37">
@@ -1482,13 +1482,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.300112</v>
+        <v>0.14701</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.008821</v>
+        <v>0.139445</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.668821</v>
+        <v>2.406621</v>
       </c>
     </row>
     <row r="49">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">

--- a/output/pdf_financials_xlsx/MHUB.xlsx
+++ b/output/pdf_financials_xlsx/MHUB.xlsx
@@ -2622,10 +2622,8 @@
       <c r="E99" s="3" t="n">
         <v>-6.482632</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="100">
@@ -2646,10 +2644,8 @@
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2670,10 +2666,8 @@
       <c r="E101" s="3" t="n">
         <v>-0.030785</v>
       </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="3" t="n">
+        <v>0.029785</v>
       </c>
     </row>
     <row r="102">
@@ -2694,10 +2688,8 @@
       <c r="E102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2718,10 +2710,8 @@
       <c r="E103" s="3" t="n">
         <v>0.05452</v>
       </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="3" t="n">
+        <v>-0.084505</v>
       </c>
     </row>
     <row r="104">
@@ -2742,10 +2732,8 @@
       <c r="E104" s="3" t="n">
         <v>0.861951</v>
       </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="3" t="n">
+        <v>-0.58172</v>
       </c>
     </row>
     <row r="105">
@@ -2766,10 +2754,8 @@
       <c r="E105" s="3" t="n">
         <v>0.237034</v>
       </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="3" t="n">
+        <v>-0.372756</v>
       </c>
     </row>
     <row r="106">
@@ -2790,10 +2776,8 @@
       <c r="E106" s="3" t="n">
         <v>1.12272</v>
       </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="3" t="n">
+        <v>-1.009196</v>
       </c>
     </row>
     <row r="107">
@@ -2814,10 +2798,8 @@
       <c r="E107" s="3" t="n">
         <v>0.325553</v>
       </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="3" t="n">
+        <v>0.515626</v>
       </c>
     </row>
     <row r="108">
@@ -2838,10 +2820,8 @@
       <c r="E108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2862,10 +2842,8 @@
       <c r="E109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2886,10 +2864,8 @@
       <c r="E110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2910,10 +2886,8 @@
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2934,10 +2908,8 @@
       <c r="E112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2958,10 +2930,8 @@
       <c r="E113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2982,10 +2952,8 @@
       <c r="E114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3006,10 +2974,8 @@
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="3" t="n">
+        <v>2.939816</v>
       </c>
     </row>
     <row r="116">
@@ -3030,10 +2996,8 @@
       <c r="E116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3054,10 +3018,8 @@
       <c r="E117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3078,10 +3040,8 @@
       <c r="E118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3102,10 +3062,8 @@
       <c r="E119" s="3" t="n">
         <v>0.351386</v>
       </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F119" s="3" t="n">
+        <v>2.939816</v>
       </c>
     </row>
     <row r="120">
@@ -3126,10 +3084,8 @@
       <c r="E120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3150,10 +3106,8 @@
       <c r="E121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3174,10 +3128,8 @@
       <c r="E122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3198,10 +3150,8 @@
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3222,10 +3172,8 @@
       <c r="E124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3246,10 +3194,8 @@
       <c r="E125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3270,10 +3216,8 @@
       <c r="E126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3326,10 +3270,8 @@
       <c r="E128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3350,10 +3292,8 @@
       <c r="E129" s="3" t="n">
         <v>7.269268</v>
       </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F129" s="3" t="n">
+        <v>0.002958</v>
       </c>
     </row>
     <row r="130">
@@ -3406,10 +3346,8 @@
       <c r="E131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3430,10 +3368,8 @@
       <c r="E132" s="3" t="n">
         <v>2.716274</v>
       </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="3" t="n">
+        <v>-3.607176</v>
       </c>
     </row>
     <row r="133">
@@ -3486,10 +3422,8 @@
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3510,10 +3444,8 @@
       <c r="E135" s="3" t="n">
         <v>-4.90438</v>
       </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="3" t="n">
+        <v>-6.54995</v>
       </c>
     </row>
   </sheetData>
@@ -3527,7 +3459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6130,10 +6062,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>January 31, 2024 January</t>
+          <t>Net loss $ (10,495,326) $</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6147,16 +6083,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="64">
@@ -6167,35 +6105,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>-3.245595</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>-9.647561</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>-8.529655999999999</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>-6.482632</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest expense and accretion 54,610</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.085455</v>
       </c>
     </row>
     <row r="65">
@@ -6206,31 +6146,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Interest expense and accretion</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>0.111585</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.275771</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.08862299999999999</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>0.114333</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization 66,912</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.107274</v>
       </c>
     </row>
     <row r="66">
@@ -6241,17 +6191,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Stock-based compensation 597,108</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6269,13 +6219,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="5" t="n">
-        <v>0.09386</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.515626</v>
       </c>
     </row>
     <row r="67">
@@ -6286,23 +6236,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Compensation warrants</t>
+          <t>Impairment of goodwill 5,570,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>0.02863</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0.425311</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>0.037201</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -6323,30 +6279,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>0.351701</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0.903644</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0.622432</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>0.325553</v>
+          <t>Loss on debt settlement 118,762</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -6362,12 +6322,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gain on debt remeasurement</t>
+          <t>Change in fair value of investment (1,191,307)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -6381,16 +6341,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="5" t="n">
-        <v>-0.052911</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>-0.090006</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>-0.020411</v>
       </c>
     </row>
     <row r="70">
@@ -6401,12 +6363,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Non-cash finance expense</t>
+          <t>Change in fair value of contingent consideration (761,117)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -6420,11 +6382,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G70" s="5" t="n">
-        <v>0.091946</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>0.011792</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6440,32 +6406,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Non-cash consulting expense 145,946</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.065217</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>-0.09019099999999999</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>-0.030785</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6481,35 +6449,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>-0.2615</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.515933</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>0.443977</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>0.05452</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unrealized foreign exchange (gains) losses (491)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0.012057</v>
       </c>
     </row>
     <row r="73">
@@ -6525,30 +6495,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>-0.09314699999999999</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>-0.231398</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>-0.024643</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>0.861951</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Receivables (12,605)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0.029785</v>
       </c>
     </row>
     <row r="74">
@@ -6564,12 +6536,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
+          <t>Prepaid expenses 16,697</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ChangeInOtherWorkingCapital</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6582,16 +6554,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G74" s="5" t="n">
-        <v>0.155488</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>0.237034</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-0.084505</v>
       </c>
     </row>
     <row r="75">
@@ -6607,30 +6581,36 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Trade payables and accrued liabilities 91,773</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>-2.871742</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-8.588082999999999</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>-7.257734</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>-4.90438</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>-0.58172</v>
       </c>
     </row>
     <row r="76">
@@ -6641,12 +6621,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cash acquired in acquisition, net of acquisition costs</t>
+          <t>Deferred revenue (45,860)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6665,13 +6645,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="5" t="n">
-        <v>0.351386</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>-0.372756</v>
       </c>
     </row>
     <row r="77">
@@ -6682,19 +6662,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Net cash provided by investing activities</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Net cash used in operating activities (5,844,898)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6710,13 +6686,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="5" t="n">
-        <v>0.351386</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-6.54995</v>
       </c>
     </row>
     <row r="78">
@@ -6727,26 +6703,34 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net of issue costs</t>
+          <t>Acquisition of Jules AI, net of cash acquired (660,373)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>2.29336</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>11.771464</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>5.454487</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>7.269268</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6762,35 +6746,41 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Loan repayment</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Proceeds from sale of investment 3,118,978</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>-0.831712</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>-0.048647</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="5" t="n">
+        <v>2.939816</v>
       </c>
     </row>
     <row r="80">
@@ -6801,35 +6791,41 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Proceeds from stock option and warrant exercises</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Net cash provided by investing activities 2,458,605</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>0.133148</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.064</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="5" t="n">
+        <v>2.939816</v>
       </c>
     </row>
     <row r="81">
@@ -6845,25 +6841,29 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>3.29336</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>11.0729</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>5.46984</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>7.269268</v>
+          <t>Proceeds from issuance of shares, net of issue costs 6,947,125</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6884,14 +6884,10 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Share issuance costs incurred pursuant to Abaxx transaction -</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -6902,16 +6898,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G82" s="5" t="n">
-        <v>-1.787894</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>2.716274</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-0.110182</v>
       </c>
     </row>
     <row r="83">
@@ -6927,26 +6925,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
+          <t>Loan repayment (1,341,560)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.034561</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.456179</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>2.940996</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>1.153102</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.645</v>
       </c>
     </row>
     <row r="84">
@@ -6962,26 +6966,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cash, ending $</t>
+          <t>Loan received 1,050,000</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.456179</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>2.940996</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>1.153102</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>3.869376</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="85">
@@ -6992,12 +7002,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Shares issued pursuant to acquisition $</t>
+          <t>Proceeds from stock option and warrant exercises 1,539,138</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -7016,13 +7026,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="5" t="n">
-        <v>1.706106</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0.30814</v>
       </c>
     </row>
     <row r="86">
@@ -7033,33 +7043,41 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Shares issued for repayment of convertible debt $</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>0.03853</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0.138305</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>0.406809</v>
+          <t>Net cash provided by financing activities 8,194,703</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I86" s="5" t="n">
+        <v>0.002958</v>
       </c>
     </row>
     <row r="87">
@@ -7068,33 +7086,43 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>January 31, 2023 January</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Increase (decrease) in cash 4,808,410</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="5" t="n">
+        <v>-3.607176</v>
       </c>
     </row>
     <row r="88">
@@ -7105,20 +7133,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Shares for services</t>
+          <t>Cash, beginning 262,200</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>0.3453</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>0.253</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7130,10 +7162,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="5" t="n">
+        <v>3.869376</v>
       </c>
     </row>
     <row r="89">
@@ -7144,12 +7174,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Loss on debt settlement</t>
+          <t>Cash, ending $ 5,070,610 $</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -7158,8 +7188,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>0.0143</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7171,10 +7203,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="5" t="n">
+        <v>0.2622</v>
       </c>
     </row>
     <row r="90">
@@ -7185,29 +7215,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Decrease in cash</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Shares issued pursuant to acquisition $ 2,081,668 $</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>2.484817</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>-1.787894</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7226,18 +7256,26 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Non-cash transactions</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>January 31, 2022 January</t>
+          <t>Shares issued for settlement of debt 447,903</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7263,17 +7301,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Loan discount</t>
+          <t>Warrants issued for settlement of debt 107,753</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>-0.045216</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7304,17 +7344,19 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Shares issued pursuant to Abaxx transaction -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>-0.002029</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7331,10 +7373,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="5" t="n">
+        <v>5.102077</v>
       </c>
     </row>
     <row r="94">
@@ -7345,37 +7385,33 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Item not effecting cash</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bonus shares</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
-        <v>0.0498</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.245595</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-9.647561</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-8.529655999999999</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-6.482632</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="95">
@@ -7386,39 +7422,35 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>-0.104654</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.065217</v>
+          <t>Interest expense and accretion</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H95" s="5" t="n">
+        <v>0.114333</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.085455</v>
       </c>
     </row>
     <row r="96">
@@ -7429,17 +7461,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Unearned revenue</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>-0.006617</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7451,15 +7489,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H96" s="5" t="n">
+        <v>0.09386</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>0.107274</v>
       </c>
     </row>
     <row r="97">
@@ -7470,17 +7504,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Loans’ proceeds</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>1</v>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7492,15 +7532,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H97" s="5" t="n">
+        <v>0.325553</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0.515626</v>
       </c>
     </row>
     <row r="98">
@@ -7511,34 +7547,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0.421618</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>2.484817</v>
+          <t>Gain on debt remeasurement</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H98" s="5" t="n">
+        <v>-0.090006</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7549,20 +7583,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Revenue 13 $ 1,362,569 $</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Change in fair value of investment</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -7584,26 +7618,26 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>2.019913</v>
+        <v>-0.020411</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cost of sales 14 1,022,395</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Non-cash finance expense</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -7619,32 +7653,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="n">
-        <v>1.162049</v>
+      <c r="H100" s="5" t="n">
+        <v>0.011792</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Item not affecting cash</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gross margin 340,174</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Unrealized foreign exchange (gains) losses</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -7666,28 +7700,28 @@
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0.857864</v>
+        <v>0.012057</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Research and development 14 2,569,759</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7695,89 +7729,75 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>-0.065217</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-0.09019099999999999</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-0.030785</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>3.067572</v>
+        <v>0.029785</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sales and marketing 14 1,214,693</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>-0.2615</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>-0.515933</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.443977</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.05452</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>1.091053</v>
+        <v>-0.084505</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>General and administrative 3,14 2,473,014</t>
+          <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7795,32 +7815,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>0.861951</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>2.204105</v>
+        <v>-0.58172</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Stock-based compensation 10,12,14 597,108</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Deferred revenue</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -7831,79 +7853,67 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="5" t="n">
+        <v>0.155488</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0.237034</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0.515626</v>
+        <v>-0.372756</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Amortization 6,14 66,912</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-2.871742</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>-8.588082999999999</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-7.257734</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>-4.90438</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.107274</v>
+        <v>-6.54995</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Total operating expenses (6,921,486)</t>
+          <t>Cash acquired in acquisition, net of acquisition costs</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -7922,32 +7932,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>-6.98563</v>
+      <c r="H107" s="5" t="n">
+        <v>0.351386</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Net loss from operations (6,581,312)</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Proceeds from sale of investment</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -7969,26 +7983,30 @@
         </is>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-6.127766</v>
+        <v>2.939816</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Interest and accretion expense 8,14 (68,499)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Net cash provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -8004,74 +8022,62 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" s="5" t="n">
+        <v>0.351386</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>-0.085455</v>
+        <v>2.939816</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Other income 832</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="n">
-        <v>0.003265</v>
+          <t>Proceeds from issuance of shares, net of issue costs</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>2.29336</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>11.771464</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>5.454487</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>7.269268</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Loss on debt settlement 8 (118,762)</t>
+          <t>Share issuance costs incurred pursuant to Abaxx transaction</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8095,26 +8101,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="5" t="n">
+        <v>-0.110182</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gain on investment 5 1,191,307</t>
+          <t>Loan repayment</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8123,15 +8127,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" s="5" t="n">
+        <v>-0.831712</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>-0.048647</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8139,23 +8139,23 @@
         </is>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0.020411</v>
+        <v>-0.645</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Impairment of goodwill 3,6 (5,570,000)</t>
+          <t>Loan received</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8179,26 +8179,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="5" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent consideration 3,9 761,117</t>
+          <t>Proceeds from stock option and warrant exercises</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8207,85 +8205,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="5" t="n">
+        <v>0.133148</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.064</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="5" t="n">
+        <v>0.30814</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss) (74,296)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>3.29336</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>11.0729</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>5.46984</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>7.269268</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>-0.05121</v>
+        <v>0.002958</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Total other income (expenses) (3,878,301)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -8296,122 +8288,96 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="5" t="n">
+        <v>-1.787894</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>2.716274</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>-0.112989</v>
+        <v>-3.607176</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Net loss before income taxes (10,459,613)</t>
+          <t>Cash, beginning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="5" t="n">
+        <v>0.034561</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.456179</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>2.940996</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>1.153102</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>-6.240755</v>
+        <v>3.869376</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Income tax expense 15 35,713</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, ending $</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>0.456179</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>2.940996</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.153102</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>3.869376</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0.2622</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $ (10,495,326) $</t>
+          <t>Shares issued pursuant to acquisition $</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -8430,29 +8396,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>-6.240755</v>
+      <c r="H119" s="5" t="n">
+        <v>1.706106</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $ (0.12) $</t>
+          <t>Shares issued pursuant to Abaxx transaction $</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -8477,23 +8443,19 @@
         </is>
       </c>
       <c r="I120" s="5" t="n">
-        <v>-9e-08</v>
+        <v>5.102077</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Weighted Average Number of Shares</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Outstanding 90,978,884</t>
+          <t>January 31, 2024 January</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -8507,78 +8469,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="5" t="n">
-        <v>72.756758</v>
+      <c r="G121" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>- 88,029 - - 281,274 459,091 - - - - - - 289,658 - 626,341 - Deficit (30,962,003) (6,240,755) (36,374,364) (10,495,326)</t>
+          <t>Interest expense and accretion</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>-45.953691</v>
+      <c r="E122" s="5" t="n">
+        <v>0.111585</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.275771</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.08862299999999999</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0.114333</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>of        Reserve       88,029  - (88,029) - - - - - - - - - - - - - - - - - -                                 Equity                                                                                    Convertible                                                           Component    Debt $                           $                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -8594,10 +8552,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H123" s="5" t="n">
+        <v>0.09386</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -8608,80 +8564,72 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2,981                                                                                                                                                                                                                               these</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2,981                                                                                                                                                                                                                               these of Amount 31,227,928 4,945,467 336,618 36,512,994 6,211,961 447,903 1,935,722 145,946 1,245,881 554,484</t>
+          <t>Compensation warrants</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="5" t="n">
+        <v>0.02863</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>0.425311</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.037201</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="5" t="n">
-        <v>47.054891</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>$                           $                     part                               Capital</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>$                           $                     part                               Capital</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0.351701</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0.903644</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.622432</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>0.325553</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -8692,17 +8640,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>$                           $                     part                               Capital</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>of Share integral</t>
+          <t>Gain on debt remeasurement</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -8716,34 +8664,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="n">
-        <v>0.0075</v>
+      <c r="G126" s="5" t="n">
+        <v>-0.052911</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>-0.090006</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>$                           $                     part                               Capital</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>an 765,664 135,135 817,500 Shares 8,840,000 1,100,928 2,513,144 3,111,726 are Number 68,134,675 18,141,838 87,049,677</t>
+          <t>Non-cash finance expense</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -8757,230 +8703,228 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="5" t="n">
-        <v>103.56811</v>
+      <c r="G127" s="5" t="n">
+        <v>0.091946</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0.011792</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>¤ Equity 10 10 10 10 10 10 10 10 10 Notes 5,10 8,10 10,12 8,10 3,10 3,10</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="n">
-        <v>0.001012</v>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>-0.09314699999999999</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>-0.231398</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-0.024643</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.861951</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Non-cash transactions</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Notes January 31, 2025 January</t>
+          <t>Shares issued for repayment of convertible debt $</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E129" s="5" t="n">
+        <v>0.03853</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>0.138305</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.406809</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Revenue 12 $</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>January 31, 2023 January</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="5" t="n">
+        <v>0.002022</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.186784</v>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>2.009166</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>2.019913</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Item not effecting cash</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cost of sales 13</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares for services</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0.253</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H131" s="5" t="n">
-        <v>1.147878</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>1.162049</v>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Item not effecting cash</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Loss on debt settlement</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="5" t="n">
+        <v>0.0143</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H132" s="5" t="n">
-        <v>0.8612880000000001</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>0.857864</v>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Research and development 13</t>
+          <t>Decrease in cash</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8988,91 +8932,77 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="n">
-        <v>4.566016</v>
-      </c>
-      <c r="I133" s="5" t="n">
-        <v>3.067572</v>
+      <c r="F133" s="5" t="n">
+        <v>2.484817</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>-1.787894</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sales and marketing 13</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>January 31, 2022 January</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H134" s="5" t="n">
-        <v>0.522286</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>1.091053</v>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>General and administrative 3,13</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loan discount</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>-0.045216</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -9084,34 +9014,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H135" s="5" t="n">
-        <v>2.730041</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>2.204105</v>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9,11,13</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E136" s="5" t="n">
+        <v>-0.002029</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -9123,38 +9055,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H136" s="5" t="n">
-        <v>0.325553</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>0.515626</v>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Item not effecting cash</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Amortization 6,13</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bonus shares</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" s="5" t="n">
+        <v>0.0498</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -9166,81 +9096,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="5" t="n">
-        <v>0.09386</v>
-      </c>
-      <c r="I137" s="5" t="n">
-        <v>0.107274</v>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>-0.104654</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.065217</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="5" t="n">
-        <v>8.237755999999999</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>6.98563</v>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net loss from operations</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Unearned revenue</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>-0.006617</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -9252,34 +9180,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H139" s="5" t="n">
-        <v>-7.376468</v>
-      </c>
-      <c r="I139" s="5" t="n">
-        <v>-6.127766</v>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Interest and accretion expense 8,13</t>
+          <t>Loans’ proceeds</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E140" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -9291,54 +9221,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="5" t="n">
-        <v>-0.114333</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>-0.085455</v>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Other income 12</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0.421618</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>2.484817</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H141" s="5" t="n">
-        <v>0.988901</v>
-      </c>
-      <c r="I141" s="5" t="n">
-        <v>0.003265</v>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -9347,17 +9281,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Gain on debt remeasurement 8</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Revenue 13 $ 1,362,569 $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -9368,16 +9302,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G142" s="5" t="n">
-        <v>0.052911</v>
-      </c>
-      <c r="H142" s="5" t="n">
-        <v>0.090006</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>2.019913</v>
       </c>
     </row>
     <row r="143">
@@ -9386,17 +9322,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gain on investment 5</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Cost of sales 14 1,022,395</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -9418,7 +9354,7 @@
         </is>
       </c>
       <c r="I143" s="5" t="n">
-        <v>0.020411</v>
+        <v>1.162049</v>
       </c>
     </row>
     <row r="144">
@@ -9427,35 +9363,39 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Other income (expenses)</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
+          <t>Gross margin 340,174</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>-0.004476</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>-0.018562</v>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>-0.060949</v>
-      </c>
-      <c r="H144" s="5" t="n">
-        <v>-0.070738</v>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I144" s="5" t="n">
-        <v>-0.05121</v>
+        <v>0.857864</v>
       </c>
     </row>
     <row r="145">
@@ -9466,17 +9406,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Total other income (expenses)</t>
+          <t>Research and development 14 2,569,759</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9489,14 +9429,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G145" s="5" t="n">
-        <v>-0.008038</v>
-      </c>
-      <c r="H145" s="5" t="n">
-        <v>0.893836</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I145" s="5" t="n">
-        <v>-0.112989</v>
+        <v>3.067572</v>
       </c>
     </row>
     <row r="146">
@@ -9507,33 +9451,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Sales and marketing 14 1,214,693</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="n">
-        <v>-3.245595</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>-9.647561</v>
-      </c>
-      <c r="G146" s="5" t="n">
-        <v>-8.529655999999999</v>
-      </c>
-      <c r="H146" s="5" t="n">
-        <v>-6.482632</v>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I146" s="5" t="n">
-        <v>-6.240755</v>
+        <v>1.091053</v>
       </c>
     </row>
     <row r="147">
@@ -9544,33 +9496,41 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>General and administrative 3,14 2,473,014</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>-1.8e-07</v>
-      </c>
-      <c r="G147" s="5" t="n">
-        <v>-2.6e-07</v>
-      </c>
-      <c r="H147" s="5" t="n">
-        <v>-1.4e-07</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I147" s="5" t="n">
-        <v>-9e-08</v>
+        <v>2.204105</v>
       </c>
     </row>
     <row r="148">
@@ -9581,12 +9541,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Outstanding 9</t>
+          <t>Stock-based compensation 10,12,14 597,108</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -9605,11 +9565,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" s="5" t="n">
-        <v>45.485866</v>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I148" s="5" t="n">
-        <v>72.756758</v>
+        <v>0.515626</v>
       </c>
     </row>
     <row r="149">
@@ -9620,15 +9582,19 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>- - - 504,426 404,755 - - - - 88,029 281,274 459,091 - Deficit (25,388,552) (6,482,632) (30,962,003)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>Amortization 6,14 66,912</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -9644,11 +9610,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="5" t="n">
-        <v>-36.374364</v>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I149" s="5" t="n">
-        <v>-6.240755</v>
+        <v>0.107274</v>
       </c>
     </row>
     <row r="150">
@@ -9659,12 +9627,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>of        Reserve       88,029 - - - - - - -       88,029 - - - (88,029) - - - -  -                                 Equity                                                                                    Convertible                                                           Component    Debt $                       $                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+          <t>Total operating expenses (6,921,486)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -9688,10 +9656,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" s="5" t="n">
+        <v>-6.98563</v>
       </c>
     </row>
     <row r="151">
@@ -9702,12 +9668,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2,981 336,618                                                                                               these</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2,981 336,618                                                                                               these of Amount 22,901,097 6,620,725 1,706,106 31,227,928</t>
+          <t>Net loss from operations (6,581,312)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -9726,11 +9692,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H151" s="5" t="n">
-        <v>36.512994</v>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I151" s="5" t="n">
-        <v>4.945467</v>
+        <v>-6.127766</v>
       </c>
     </row>
     <row r="152">
@@ -9741,12 +9709,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>$                       $           7                                                                                                                                                                                   part                               Capital</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>$                       $           7                                                                                                                                                                                   part                               Capital</t>
+          <t>Interest and accretion expense 8,14 (68,499)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -9770,10 +9738,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="5" t="n">
+        <v>-0.085455</v>
       </c>
     </row>
     <row r="153">
@@ -9782,13 +9748,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Notes January 31, 2024 January</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Other income 832</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -9799,16 +9773,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G153" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="H153" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>0.003265</v>
       </c>
     </row>
     <row r="154">
@@ -9819,12 +9795,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Payroll and contractor expenses 11</t>
+          <t>Loss on debt settlement 8 (118,762)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -9838,11 +9814,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G154" s="5" t="n">
-        <v>3.337546</v>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>5.959097</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -9858,19 +9838,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Professional fees 3</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Gain on investment 5 1,191,307</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -9881,16 +9857,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" s="5" t="n">
-        <v>0.256126</v>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>0.636234</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>0.020411</v>
       </c>
     </row>
     <row r="156">
@@ -9901,30 +9879,34 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="n">
-        <v>0.09550500000000001</v>
-      </c>
-      <c r="F156" s="5" t="n">
-        <v>0.525521</v>
-      </c>
-      <c r="G156" s="5" t="n">
-        <v>0.718464</v>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>0.635746</v>
+          <t>Impairment of goodwill 3,6 (5,570,000)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9940,30 +9922,34 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="n">
-        <v>0.010221</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>0.419105</v>
-      </c>
-      <c r="G157" s="5" t="n">
-        <v>0.36907</v>
-      </c>
-      <c r="H157" s="5" t="n">
-        <v>0.475449</v>
+          <t>Change in fair value of contingent consideration 3,9 761,117</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9979,19 +9965,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Consulting 9,11</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain (loss) (74,296)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -10002,16 +9984,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G158" s="5" t="n">
-        <v>0.626047</v>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>0.367871</v>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>-0.05121</v>
       </c>
     </row>
     <row r="159">
@@ -10022,12 +10006,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Administrative services 11</t>
+          <t>Total other income (expenses) (3,878,301)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -10041,16 +10025,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G159" s="5" t="n">
-        <v>0.203232</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>0.231245</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>-0.112989</v>
       </c>
     </row>
     <row r="160">
@@ -10061,19 +10047,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Management fees 11</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Net loss before income taxes (10,459,613)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -10084,16 +10066,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G160" s="5" t="n">
-        <v>0.53243</v>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>0.280066</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="161">
@@ -10104,15 +10088,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Development costs 4</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Income tax expense 15 35,713</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -10123,11 +10111,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G161" s="5" t="n">
-        <v>1.737331</v>
-      </c>
-      <c r="H161" s="5" t="n">
-        <v>0.20681</v>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -10143,35 +10135,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>0.008848999999999999</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>0.007861</v>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>0.142798</v>
-      </c>
-      <c r="H162" s="5" t="n">
-        <v>0.100773</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net and comprehensive loss $ (10,495,326) $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="163">
@@ -10182,35 +10176,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in fair value of contingent</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n">
-        <v>0.001124</v>
-      </c>
-      <c r="F163" s="5" t="n">
-        <v>0.121096</v>
-      </c>
-      <c r="G163" s="5" t="n">
-        <v>0.0743</v>
-      </c>
-      <c r="H163" s="5" t="n">
-        <v>0.07292999999999999</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share – basic and diluted $ (0.12) $</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>-9e-08</v>
       </c>
     </row>
     <row r="164">
@@ -10221,12 +10217,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted Average Number of Shares</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9,11</t>
+          <t>Outstanding 90,978,884</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -10240,16 +10236,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G164" s="5" t="n">
-        <v>0.622432</v>
-      </c>
-      <c r="H164" s="5" t="n">
-        <v>0.325553</v>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>72.756758</v>
       </c>
     </row>
     <row r="165">
@@ -10260,12 +10258,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted Average Number of Shares</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Interest and accretion expense 8</t>
+          <t>- 88,029 - - 281,274 459,091 - - - - - - 289,658 - 626,341 - Deficit (30,962,003) (6,240,755) (36,374,364) (10,495,326)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -10279,16 +10277,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G165" s="5" t="n">
-        <v>0.088626</v>
-      </c>
-      <c r="H165" s="5" t="n">
-        <v>0.114333</v>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>-45.953691</v>
       </c>
     </row>
     <row r="166">
@@ -10299,19 +10299,15 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted Average Number of Shares</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Amortization 6</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>of        Reserve       88,029  - (88,029) - - - - - - - - - - - - - - - - - -                                 Equity                                                                                    Convertible                                                           Component    Debt $                           $                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -10327,8 +10323,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H166" s="5" t="n">
-        <v>0.09386</v>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -10344,19 +10342,15 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>2,981                                                                                                                                                                                                                               these</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>2,981                                                                                                                                                                                                                               these of Amount 31,227,928 4,945,467 336,618 36,512,994 6,211,961 447,903 1,935,722 145,946 1,245,881 554,484</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -10367,16 +10361,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G167" s="5" t="n">
-        <v>8.708402</v>
-      </c>
-      <c r="H167" s="5" t="n">
-        <v>9.499967</v>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>47.054891</v>
       </c>
     </row>
     <row r="168">
@@ -10387,19 +10383,15 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$                           $                     part                               Capital</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Net loss from operations</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>$                           $                     part                               Capital</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -10410,11 +10402,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G168" s="5" t="n">
-        <v>-8.521618</v>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>-7.490801</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -10430,12 +10426,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>$                           $                     part                               Capital</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Outstanding 16</t>
+          <t>of Share integral</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -10449,16 +10445,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G169" s="5" t="n">
-        <v>33.380979</v>
-      </c>
-      <c r="H169" s="5" t="n">
-        <v>46.485866</v>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.0075</v>
       </c>
     </row>
     <row r="170">
@@ -10469,12 +10467,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>$                           $                     part                               Capital</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares total</t>
+          <t>an 765,664 135,135 817,500 Shares 8,840,000 1,100,928 2,513,144 3,111,726 are Number 68,134,675 18,141,838 87,049,677</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -10498,10 +10496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I170" s="5" t="n">
+        <v>103.56811</v>
       </c>
     </row>
     <row r="171">
@@ -10512,12 +10508,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>37,201 64,000                                                                                                                                                                41,063               325,553                                                                                                                                                                                                                                                                                                                2,768,013                                                                              (Deficit)          1,910,750          5,454,487 390,504                              622,432                 (50,282)                                 Total                                                                                                                                           (8,529,656)                               7,228,205 1,706,106                                                 (6,482,632)                                                                                                   Shareholders’              $                                                    Equity                        $</t>
+          <t>¤ Equity 10 10 10 10 10 10 10 10 10 Notes 5,10 8,10 10,12 8,10 3,10 3,10</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -10541,10 +10537,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I171" s="5" t="n">
+        <v>0.001012</v>
       </c>
     </row>
     <row r="172">
@@ -10553,14 +10547,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Weighted Average Number of Shares</t>
-        </is>
-      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>370,569 155,771 504,426 404,755 Deficit (17,385,236) (8,529,656) (25,388,552)</t>
+          <t>Notes January 31, 2025 January</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -10574,16 +10564,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" s="5" t="n">
-        <v>-30.962003</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>-6.482632</v>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="173">
@@ -10592,17 +10582,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Weighted Average Number of Shares</t>
-        </is>
-      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>of - - - - -</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Revenue 12 $</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -10613,20 +10603,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G173" s="5" t="n">
+        <v>0.186784</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>2.009166</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>2.019913</v>
       </c>
     </row>
     <row r="174">
@@ -10635,17 +10619,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements</t>
-        </is>
-      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Cost of sales 13</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -10661,15 +10645,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H174" s="5" t="n">
+        <v>1.147878</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>1.162049</v>
       </c>
     </row>
     <row r="175">
@@ -10678,17 +10658,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements</t>
-        </is>
-      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements total</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -10704,15 +10684,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H175" s="5" t="n">
+        <v>0.8612880000000001</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>0.857864</v>
       </c>
     </row>
     <row r="176">
@@ -10723,15 +10699,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>- - - - -                                                               these</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>- - - - -      - - - - -               of                                                                                                                                                                                                                                                                                                integral                      Share an 810,000 100,000 Shares 60,603,493 77,613,493 8,176,634 are (Deficit) Number 16,100,000</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
+          <t>Research and development 13</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -10742,16 +10722,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G176" s="5" t="n">
-        <v>136.269368</v>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>50.479241</v>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.566016</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>3.067572</v>
       </c>
     </row>
     <row r="177">
@@ -10760,33 +10740,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Notes January 31, 2023 January</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Sales and marketing 13</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F177" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="G177" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>0.522286</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>1.091053</v>
       </c>
     </row>
     <row r="178">
@@ -10795,37 +10783,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Revenue $</t>
+          <t>General and administrative 3,13</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="n">
-        <v>0.067367</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G178" s="5" t="n">
-        <v>0.186784</v>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>2.730041</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>2.204105</v>
       </c>
     </row>
     <row r="179">
@@ -10836,33 +10828,35 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Administrative services 10</t>
+          <t>Stock-based compensation 9,11,13</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>0.0645</v>
-      </c>
-      <c r="G179" s="5" t="n">
-        <v>0.203232</v>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="n">
+        <v>0.325553</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>0.515626</v>
       </c>
     </row>
     <row r="180">
@@ -10873,37 +10867,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Consulting 8</t>
+          <t>Amortization 6,13</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>0.056419</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>1.495364</v>
-      </c>
-      <c r="G180" s="5" t="n">
-        <v>1.56635</v>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>0.09386</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>0.107274</v>
       </c>
     </row>
     <row r="181">
@@ -10914,33 +10910,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Finance expense 8</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" s="5" t="n">
-        <v>0.07843</v>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>0.473215</v>
-      </c>
-      <c r="G181" s="5" t="n">
-        <v>0.178697</v>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>8.237755999999999</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>6.98563</v>
       </c>
     </row>
     <row r="182">
@@ -10951,33 +10953,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Interest expense and accretion 6,7</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" s="5" t="n">
-        <v>0.111585</v>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>0.275777</v>
-      </c>
-      <c r="G182" s="5" t="n">
-        <v>0.088626</v>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss from operations</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>-7.376468</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>-6.127766</v>
       </c>
     </row>
     <row r="183">
@@ -10988,33 +10996,35 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Development costs 3</t>
+          <t>Interest and accretion expense 8,13</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
-      <c r="E183" s="5" t="n">
-        <v>1.665896</v>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>3.638697</v>
-      </c>
-      <c r="G183" s="5" t="n">
-        <v>1.737331</v>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>-0.114333</v>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>-0.085455</v>
       </c>
     </row>
     <row r="184">
@@ -11025,37 +11035,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Management fees 10</t>
+          <t>Other income 12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E184" s="5" t="n">
-        <v>0.463994</v>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>0.704912</v>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>0.53243</v>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>0.988901</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>0.003265</v>
       </c>
     </row>
     <row r="185">
@@ -11066,28 +11078,30 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Payroll expenses 10</t>
+          <t>Gain on debt remeasurement 8</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" s="5" t="n">
-        <v>0.06708</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>0.484129</v>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>0.949296</v>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.052911</v>
+      </c>
+      <c r="H185" s="5" t="n">
+        <v>0.090006</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11103,37 +11117,37 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E186" s="5" t="n">
-        <v>0.213993</v>
-      </c>
-      <c r="F186" s="5" t="n">
-        <v>0.500878</v>
-      </c>
-      <c r="G186" s="5" t="n">
-        <v>0.256126</v>
+          <t>Gain on investment 5</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I186" s="5" t="n">
+        <v>0.020411</v>
       </c>
     </row>
     <row r="187">
@@ -11144,33 +11158,33 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8,10</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
-        <v>0.351701</v>
+        <v>-0.004476</v>
       </c>
       <c r="F187" s="5" t="n">
-        <v>0.903644</v>
+        <v>-0.018562</v>
       </c>
       <c r="G187" s="5" t="n">
-        <v>0.622432</v>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.060949</v>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>-0.070738</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>-0.05121</v>
       </c>
     </row>
     <row r="188">
@@ -11181,37 +11195,37 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Total other income (expenses)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E188" s="5" t="n">
-        <v>3.353702</v>
-      </c>
-      <c r="F188" s="5" t="n">
-        <v>9.614699</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>8.708402</v>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008038</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>0.893836</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>-0.112989</v>
       </c>
     </row>
     <row r="189">
@@ -11227,32 +11241,28 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Loss on debt settlement 6</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>-3.245595</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>-0.0143</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9.647561</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>-8.529655999999999</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>-6.482632</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="190">
@@ -11268,32 +11278,28 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Gain on debt modification 7</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>-1.8e-07</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>0.052911</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.6e-07</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>-1.4e-07</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>-9e-08</v>
       </c>
     </row>
     <row r="191">
@@ -11304,39 +11310,35 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Weighted Average Number of Shares</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Outstanding 9</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F191" s="5" t="n">
-        <v>-0.018562</v>
-      </c>
-      <c r="G191" s="5" t="n">
-        <v>-0.060949</v>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>45.485866</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>72.756758</v>
       </c>
     </row>
     <row r="192">
@@ -11347,37 +11349,35 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Weighted Average Number of Shares</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E192" s="5" t="n">
-        <v>0.04074</v>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>0.032862</v>
-      </c>
-      <c r="G192" s="5" t="n">
-        <v>0.008038</v>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>- - - 504,426 404,755 - - - - 88,029 281,274 459,091 - Deficit (25,388,552) (6,482,632) (30,962,003)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>-36.374364</v>
+      </c>
+      <c r="I192" s="5" t="n">
+        <v>-6.240755</v>
       </c>
     </row>
     <row r="193">
@@ -11393,18 +11393,24 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Outstanding – basic and diluted</t>
+          <t>of        Reserve       88,029 - - - - - - -       88,029 - - - (88,029) - - - -  -                                 Equity                                                                                    Convertible                                                           Component    Debt $                       $                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" s="5" t="n">
-        <v>39.157607</v>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>53.461536</v>
-      </c>
-      <c r="G193" s="5" t="n">
-        <v>66.76195800000001</v>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -11425,12 +11431,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>2,981 336,618                                                                                               these</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>(50,282)                     - 8,125 - 853,644                                         390,504 37,201 64,000 - - 622,432                                                                              (Deficit)    -         (96,050) 253,000 116,565 425,311 125,023                                 Total                                                                                                                                                                                                                                                          1,910,750            5,454,487                                                                     (8,529,656)                                                                                                                      (1,948,822)           11,821,514                                                                                                                              (9,647,561)                                                                                                   Shareholders’                               $                                                    Equity $</t>
+          <t>2,981 336,618                                                                                               these of Amount 22,901,097 6,620,725 1,706,106 31,227,928</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -11449,15 +11455,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H194" s="5" t="n">
+        <v>36.512994</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>4.945467</v>
       </c>
     </row>
     <row r="195">
@@ -11468,12 +11470,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Shares</t>
+          <t>$                       $           7                                                                                                                                                                                   part                               Capital</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>370,569 155,771 Deficit (7,737,675) (9,647,561) (8,529,656)</t>
+          <t>$                       $           7                                                                                                                                                                                   part                               Capital</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -11482,11 +11484,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F195" s="5" t="n">
-        <v>-17.385236</v>
-      </c>
-      <c r="G195" s="5" t="n">
-        <v>-25.388552</v>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -11505,14 +11511,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
-        </is>
-      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+          <t>Notes January 31, 2024 January</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -11526,15 +11528,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G196" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -11550,12 +11548,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements total</t>
+          <t>Payroll and contractor expenses 11</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -11569,15 +11567,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G197" s="5" t="n">
+        <v>3.337546</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>5.959097</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -11593,30 +11587,34 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>$                                                                                           Compensation</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>38,301 8,125 5,996 64,000 (96,050) 253,000 143,739 125,023 406,809 these 22,901,097 Amount of 5,232,840 11,517,971</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Professional fees 3</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>5.201343</v>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>17.228945</v>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.256126</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>0.636234</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -11632,34 +11630,30 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>$                                   5                               Capital                                                                                                                                                             part</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>$                                   5                               Capital                                                                                                                                                             part</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="n">
+        <v>0.09550500000000001</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>0.525521</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.718464</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>0.635746</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -11675,34 +11669,30 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>$                                   5                               Capital                                                                                                                                                             part</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>of - - -</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>0.010221</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>0.419105</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="H200" s="5" t="n">
+        <v>0.475449</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -11716,28 +11706,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Notes January 31, 2022 January</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Consulting 9,11</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>0.626047</v>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>0.367871</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -11758,27 +11756,25 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>License fee</t>
+          <t>Administrative services 11</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" s="5" t="n">
-        <v>0.158905</v>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G202" s="5" t="n">
+        <v>0.203232</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>0.231245</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -11794,34 +11790,1767 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Management fees 11</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>0.53243</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>0.280066</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Development costs 4</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>1.737331</v>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>0.20681</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>0.008848999999999999</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>0.007861</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>0.142798</v>
+      </c>
+      <c r="H205" s="5" t="n">
+        <v>0.100773</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Regulatory fees</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>0.001124</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.121096</v>
+      </c>
+      <c r="G206" s="5" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="H206" s="5" t="n">
+        <v>0.07292999999999999</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 9,11</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>0.622432</v>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>0.325553</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Interest and accretion expense 8</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>0.088626</v>
+      </c>
+      <c r="H208" s="5" t="n">
+        <v>0.114333</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Amortization 6</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>0.09386</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>8.708402</v>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>9.499967</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Net loss from operations</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>-8.521618</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>-7.490801</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Outstanding 16</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>33.380979</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>46.485866</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares total</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>37,201 64,000                                                                                                                                                                41,063               325,553                                                                                                                                                                                                                                                                                                                2,768,013                                                                              (Deficit)          1,910,750          5,454,487 390,504                              622,432                 (50,282)                                 Total                                                                                                                                           (8,529,656)                               7,228,205 1,706,106                                                 (6,482,632)                                                                                                   Shareholders’              $                                                    Equity                        $</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>370,569 155,771 504,426 404,755 Deficit (17,385,236) (8,529,656) (25,388,552)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>-30.962003</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>-6.482632</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>of - - - - -</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>$          $                                                                                    Convertible                                                           Component    Debt                                                                                                                                                                                                                                                                                                                                                              statements total</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>- - - - -                                                               these</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>- - - - -      - - - - -               of                                                                                                                                                                                                                                                                                                integral                      Share an 810,000 100,000 Shares 60,603,493 77,613,493 8,176,634 are (Deficit) Number 16,100,000</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="n">
+        <v>136.269368</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>50.479241</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Notes January 31, 2023 January</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Revenue $</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>0.067367</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="n">
+        <v>0.186784</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Administrative services 10</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>0.203232</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Consulting 8</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>0.056419</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>1.495364</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>1.56635</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Finance expense 8</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="5" t="n">
+        <v>0.07843</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>0.473215</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>0.178697</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Interest expense and accretion 6,7</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>0.111585</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>0.275777</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>0.088626</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Development costs 3</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" s="5" t="n">
+        <v>1.665896</v>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>3.638697</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>1.737331</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Management fees 10</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="n">
+        <v>0.463994</v>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>0.704912</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>0.53243</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Payroll expenses 10</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" s="5" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>0.484129</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.949296</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>0.213993</v>
+      </c>
+      <c r="F229" s="5" t="n">
+        <v>0.500878</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>0.256126</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 8,10</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" s="5" t="n">
+        <v>0.351701</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>0.903644</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>0.622432</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>3.353702</v>
+      </c>
+      <c r="F231" s="5" t="n">
+        <v>9.614699</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>8.708402</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
           <t>Other income (expenses)</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Loss on debt settlement 6</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Gain on debt modification 7</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>0.052911</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>-0.018562</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>-0.060949</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Other income (expenses) total</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="n">
+        <v>0.04074</v>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.032862</v>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>0.008038</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" s="5" t="n">
+        <v>39.157607</v>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>53.461536</v>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>66.76195800000001</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>(50,282)                     - 8,125 - 853,644                                         390,504 37,201 64,000 - - 622,432                                                                              (Deficit)    -         (96,050) 253,000 116,565 425,311 125,023                                 Total                                                                                                                                                                                                                                                          1,910,750            5,454,487                                                                     (8,529,656)                                                                                                                      (1,948,822)           11,821,514                                                                                                                              (9,647,561)                                                                                                   Shareholders’                               $                                                    Equity $</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>370,569 155,771 Deficit (7,737,675) (9,647,561) (8,529,656)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="n">
+        <v>-17.385236</v>
+      </c>
+      <c r="G238" s="5" t="n">
+        <v>-25.388552</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>$                                                                                    Convertible                                   Debt $                                                           Component                                                                                                                                                                                                                                                                                                                                                                                                                                                              statements total</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>$                                                                                           Compensation</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>38,301 8,125 5,996 64,000 (96,050) 253,000 143,739 125,023 406,809 these 22,901,097 Amount of 5,232,840 11,517,971</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>5.201343</v>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>17.228945</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>$                                   5                               Capital                                                                                                                                                             part</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>$                                   5                               Capital                                                                                                                                                             part</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>$                                   5                               Capital                                                                                                                                                             part</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>of - - -</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Notes January 31, 2022 January</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>License fee</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" s="5" t="n">
+        <v>0.158905</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>Loan discount 6</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" s="5" t="n">
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" s="5" t="n">
         <v>0.045216</v>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
